--- a/data/content-review-batches/19_rows_181-190.xlsx
+++ b/data/content-review-batches/19_rows_181-190.xlsx
@@ -630,8 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>הכנה:
-בקערת מיקסר נשים קמח, שמרים וסוכר ונערבב דקה
+          <t xml:space="preserve">הכנה: בקערת מיקסר נשים קמח, שמרים וסוכר ונערבב דקה
 אפשר גם לערבב עם כף
 אחר כך נוסיף את הביצה, השמנת והחלב ונלוש 5 דקות
 אחרי שנראה שהבצק מתאחד נוסיף בהדרגה את החמאה
@@ -641,18 +640,18 @@
 כדי לבדוק אם הבצק סיים את הלישה תבדקו האם יש בבצק רשת גלוטן
 אם אתם לא בטוחים עדיף ללוש את הבצק עוד קצת
 אחרי שהבצק סיים את הלישה שלו נניח אותו בקערה משומנת
-ונשים את הבצק להתפחת לילה במקרר למינימום 8 שעות 
-אחרי 8 שעות נוציא את הבצק מהמקרר וישר נתחיל לעבוד איתו 
+ונשים את הבצק להתפחת לילה במקרר למינימום 8 שעות
+אחרי 8 שעות נוציא את הבצק מהמקרר וישר נתחיל לעבוד איתו
 *מהבצק יוצאות 2 רולדות אז בזמן שאתם עובדים על רולדה אחת את החלק השני של הבצק תשאירו במקרר
 להכנת המילוי מערבבים גבינה לבנה, חלבון ביצה, אינסטנט פודינג, סוכר ומחית וניל עד לקבלת קרם חלק
-מרדדים את הבצק למלבן וחותכים באמצע 
-מורחים את המילוי באופן אחיד ומגלגלים כל חלק לרולדה 
+מרדדים את הבצק למלבן וחותכים באמצע
+מורחים את המילוי באופן אחיד ומגלגלים כל חלק לרולדה
 ואז מלפפים את 2 הרולדות
 מעבירים לתבנית ומתפיחים עד להכפלת הנפח
-מורחים ביצה ואופים בתנור שחומם מראש ל-170 מעלות עד הזהבה 
+מורחים ביצה ואופים בתנור שחומם מראש ל-170 מעלות עד הזהבה
 מערבבים מים רותחים וסוכר עד שהסוכר נמס
-מיד כשהרולדה יוצאת מהתנור מברישים בסירופ סוכר 
-שימו לב שהסירופ סוכר צריך להיות קר כשמברישים אותו על העוגה 
+מיד כשהרולדה יוצאת מהתנור מברישים בסירופ סוכר
+שימו לב שהסירופ סוכר צריך להיות קר כשמברישים אותו על העוגה
 בתאבון 🤍</t>
         </is>
       </c>
@@ -906,20 +905,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>אופן ההכנה:
-הכנת התחתית:
-מערבבים את הקורנפלקס הטחון עם החמאה המומסת עד לקבלת תערובת אחידה.
+          <t xml:space="preserve">אופן ההכנה:
+הכנת התחתית: מערבבים את הקורנפלקס הטחון עם החמאה המומסת עד לקבלת תערובת אחידה.
 מהדקים לתבנית ומכניסים למקפיא בזמן הכנת המלית.
-הכנת המלית:
-מקציפים את השמנת המתוקה לקצפת יציבה.
+הכנת המלית: מקציפים את השמנת המתוקה לקצפת יציבה.
 מוסיפים את החלב המרוכז ואת מחית הווניל ומקפלים בעדינות עד לקבלת תערובת אחידה.
 יוצקים מעל שכבת התחתית ומיישרים.
 מכניסים למקפיא ללילה או לפחות ל-8 שעות.
-הכנת הציפוי:
-ממיסים את השוקולד הלבן עם השמן עד לקבלת תערובת חלקה.
+הכנת הציפוי: ממיסים את השוקולד הלבן עם השמן עד לקבלת תערובת חלקה.
 מוסיפים את הקורנפלקס המרוסק ומערבבים היטב.
-הרכבה:
-מחלצים את הכל מהתבנית וחותכים לקוביות.
+הרכבה: מחלצים את הכל מהתבנית וחותכים לקוביות.
 טובלים כל גלידונית בציפוי השוקולד הלבן והקורנפלקס.
 מחזירים למקפיא לכ-15 דקות עד שהציפוי מתייצב.
 שומרים במקפיא עד להגשה.
@@ -1084,9 +1079,10 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>אופן ההכנה:
+          <t xml:space="preserve">אופן ההכנה:
 מקציפים שמנת וסוכר לקצפת רכה. מוסיפים אינסטנט פודינג וגבינה ומקציפים לקרם יציב. מקפלים פנימה את האוראו.
-מרפדים קערה בניילון נצמד. טובלים ביסקוויטים בחלב ומסדרים שכבה בתחתית, ואז שכבות של קרם וביסקוויטים עד למילוי הקערה. מסיימים בביסקוויטים. סוגרים בניילון ומקפיאים למשך לילה, עד לקיפאון מלא.
+מרפדים קערה בניילון נצמד. טובלים ביסקוויטים בחלב ומסדרים שכבה בתחתית, ואז שכבות של קרם וביסקוויטים עד למילוי הקערה. מסיימים בביסקוויטים.
+סוגרים בניילון ומקפיאים למשך לילה, עד לקיפאון מלא.
 ממיסים יחד את חומרי הגנאש ומצננים מעט. מחלצים את העוגה, הופכים על רשת ויוצקים את הגנאש. אפשר להקפיא כ־10 דקות ולצפות בשכבה נוספת. מעבירים למקרר למשך לילה לפני ההגשה.
 לפי גודל הקערה עשויים להישאר קרם או גנאש לקינוחים אישיים. מומלץ להשתמש בקערת נירוסטה או סיליקון, לצפות כשהעוגה קפואה והגנאש קריר ומסמיך.</t>
         </is>
@@ -1169,14 +1165,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>אופן ההכנה:
-הכנת הבצק:
-מערבבים את החמאה עם הסוכר החום והסוכר הלבן 
+          <t xml:space="preserve">אופן ההכנה:
+הכנת הבצק: מערבבים את החמאה עם הסוכר החום והסוכר הלבן
 מוסיפים את הביצה ותמצית הווניל ומערבבים עד לאיחוד.
 מוסיפים את הקמח, הקקאו, אבקת האפייה והמלח ומערבבים עד לקבלת בצק אחיד.
 מוסיפים את פצפוצי השוקולד הלבן ומערבבים לפיזור אחיד.
-עיצוב ואפייה:
-שמים את הבלילה בשקית זילוף ומזלפים כדורים קטנים או יוצרים כדורים קטנטנים עם ידיים (מושלם לפעילות עם הילדים!) ומניחים על תבנית מרופדת בנייר אפייה.
+עיצוב ואפייה: שמים את הבלילה בשקית זילוף ומזלפים כדורים קטנים או יוצרים כדורים קטנטנים עם ידיים (מושלם לפעילות עם הילדים!) ומניחים על תבנית מרופדת בנייר אפייה.
 אופים בתנור שחומם מראש ל-170 מעלות במשך 6-7 דקות.(מאוד משתנה בין תנור לתנור)
 מצננים לחלוטין עד שהעוגיות הופכות פריכות.
 העוגיות נאכלות כמו קורנפלקס כי הן מיני.</t>
